--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>33.32578024511993</v>
+      </c>
+      <c r="C2">
         <v>27.04316589913962</v>
-      </c>
-      <c r="C2">
-        <v>33.32578024511993</v>
       </c>
       <c r="D2">
         <v>3.69779190694465</v>
       </c>
       <c r="E2">
+        <v>20.7806941720137</v>
+      </c>
+      <c r="F2">
+        <v>62.35621197513216</v>
+      </c>
+      <c r="G2">
         <v>16.86309385285415</v>
-      </c>
-      <c r="F2">
-        <v>62.35621197513215</v>
-      </c>
-      <c r="G2">
-        <v>20.7806941720137</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>39.14141414141415</v>
+      </c>
+      <c r="C3">
         <v>60.35353535353535</v>
-      </c>
-      <c r="C3">
-        <v>39.14141414141415</v>
       </c>
       <c r="D3">
         <v>1.656903765690377</v>
       </c>
       <c r="E3">
-        <v>30.25316455696203</v>
+        <v>19.62025316455696</v>
       </c>
       <c r="F3">
         <v>50.12658227848102</v>
       </c>
       <c r="G3">
-        <v>19.62025316455696</v>
+        <v>30.25316455696203</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>37.58389261744966</v>
+      </c>
+      <c r="C4">
         <v>34.09395973154362</v>
-      </c>
-      <c r="C4">
-        <v>37.58389261744966</v>
       </c>
       <c r="D4">
         <v>2.933070866141732</v>
       </c>
       <c r="E4">
+        <v>21.8921032056294</v>
+      </c>
+      <c r="F4">
+        <v>58.24863174354965</v>
+      </c>
+      <c r="G4">
         <v>19.85926505082095</v>
-      </c>
-      <c r="F4">
-        <v>58.24863174354964</v>
-      </c>
-      <c r="G4">
-        <v>21.8921032056294</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>41.2280701754386</v>
+      </c>
+      <c r="C5">
         <v>35.96491228070175</v>
-      </c>
-      <c r="C5">
-        <v>41.2280701754386</v>
       </c>
       <c r="D5">
         <v>2.780487804878049</v>
       </c>
       <c r="E5">
-        <v>20.2970297029703</v>
+        <v>23.26732673267327</v>
       </c>
       <c r="F5">
         <v>56.43564356435643</v>
       </c>
       <c r="G5">
-        <v>23.26732673267327</v>
+        <v>20.2970297029703</v>
       </c>
     </row>
   </sheetData>
